--- a/artfynd/A 11710-2025 artfynd.xlsx
+++ b/artfynd/A 11710-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -903,6 +903,514 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123219490</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Torpsjön, Torpsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>513031</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6702372</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På tall.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123218719</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79876</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Torpsjön, Torpsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>512908</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6702264</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123219686</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Torpsjön, Torpsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>513016</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6702423</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123219381</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Torpsjön, Torpsjön, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>513011</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6702358</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en yta av ca 10x10m</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11710-2025 artfynd.xlsx
+++ b/artfynd/A 11710-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123219490</v>
+        <v>123218719</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,49 +917,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513031</v>
+        <v>512908</v>
       </c>
       <c r="R4" t="n">
-        <v>6702372</v>
+        <v>6702264</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +980,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,12 +990,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tall.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +999,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123218719</v>
+        <v>123219490</v>
       </c>
       <c r="B5" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,38 +1029,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512908</v>
+        <v>513031</v>
       </c>
       <c r="R5" t="n">
-        <v>6702264</v>
+        <v>6702372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1113,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,6 +1127,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,7 +1146,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123219686</v>
+        <v>123219381</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1194,16 +1194,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513016</v>
+        <v>513011</v>
       </c>
       <c r="R6" t="n">
-        <v>6702423</v>
+        <v>6702358</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,12 +1250,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>På en yta av ca 10x10m</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,7 +1282,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123219381</v>
+        <v>123219686</v>
       </c>
       <c r="B7" t="n">
         <v>98365</v>
@@ -1312,12 +1317,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1325,21 +1330,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513011</v>
+        <v>513016</v>
       </c>
       <c r="R7" t="n">
-        <v>6702358</v>
+        <v>6702423</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en yta av ca 10x10m</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 11710-2025 artfynd.xlsx
+++ b/artfynd/A 11710-2025 artfynd.xlsx
@@ -1017,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123219490</v>
+        <v>123219381</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,49 +1029,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513031</v>
+        <v>513011</v>
       </c>
       <c r="R5" t="n">
-        <v>6702372</v>
+        <v>6702358</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På en yta av ca 10x10m</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,7 +1135,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,7 +1153,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123219381</v>
+        <v>123219686</v>
       </c>
       <c r="B6" t="n">
         <v>98365</v>
@@ -1181,12 +1188,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1194,21 +1201,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513011</v>
+        <v>513016</v>
       </c>
       <c r="R6" t="n">
-        <v>6702358</v>
+        <v>6702423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1242,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,12 +1252,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På en yta av ca 10x10m</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,10 +1284,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123219686</v>
+        <v>123219490</v>
       </c>
       <c r="B7" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,52 +1296,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513016</v>
+        <v>513031</v>
       </c>
       <c r="R7" t="n">
-        <v>6702423</v>
+        <v>6702372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1381,12 +1380,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,6 +1394,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11710-2025 artfynd.xlsx
+++ b/artfynd/A 11710-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123218719</v>
+        <v>123219381</v>
       </c>
       <c r="B4" t="n">
-        <v>79876</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,38 +917,57 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>512908</v>
+        <v>513011</v>
       </c>
       <c r="R4" t="n">
-        <v>6702264</v>
+        <v>6702358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -990,7 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en yta av ca 10x10m</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123219381</v>
+        <v>123219686</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1052,12 +1076,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1065,21 +1089,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513011</v>
+        <v>513016</v>
       </c>
       <c r="R5" t="n">
-        <v>6702358</v>
+        <v>6702423</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1140,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På en yta av ca 10x10m</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1172,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123219686</v>
+        <v>123218719</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>79876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,52 +1184,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513016</v>
+        <v>512908</v>
       </c>
       <c r="R6" t="n">
-        <v>6702423</v>
+        <v>6702264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,7 +1247,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1252,12 +1257,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 11710-2025 artfynd.xlsx
+++ b/artfynd/A 11710-2025 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>123219381</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
         <v>123219686</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>123218719</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>79879</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>123219490</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 11710-2025 artfynd.xlsx
+++ b/artfynd/A 11710-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123219381</v>
+        <v>123219490</v>
       </c>
       <c r="B4" t="n">
-        <v>98368</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,57 +917,49 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513011</v>
+        <v>513031</v>
       </c>
       <c r="R4" t="n">
-        <v>6702358</v>
+        <v>6702372</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +991,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,12 +1001,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en yta av ca 10x10m</t>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,6 +1015,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1041,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123219686</v>
+        <v>123218719</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>79881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,52 +1046,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513016</v>
+        <v>512908</v>
       </c>
       <c r="R5" t="n">
-        <v>6702423</v>
+        <v>6702264</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1130,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,12 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1172,10 +1146,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123218719</v>
+        <v>123219686</v>
       </c>
       <c r="B6" t="n">
-        <v>79879</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1184,38 +1158,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>512908</v>
+        <v>513016</v>
       </c>
       <c r="R6" t="n">
-        <v>6702264</v>
+        <v>6702423</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1257,7 +1245,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123219490</v>
+        <v>123219381</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,49 +1289,57 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513031</v>
+        <v>513011</v>
       </c>
       <c r="R7" t="n">
-        <v>6702372</v>
+        <v>6702358</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1370,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,12 +1381,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På en yta av ca 10x10m</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,7 +1395,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11710-2025 artfynd.xlsx
+++ b/artfynd/A 11710-2025 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123219490</v>
+        <v>123219381</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -917,49 +917,57 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513031</v>
+        <v>513011</v>
       </c>
       <c r="R4" t="n">
-        <v>6702372</v>
+        <v>6702358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1001,12 +1009,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På tall.</t>
+          <t>På en yta av ca 10x10m</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,7 +1023,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123218719</v>
+        <v>123219490</v>
       </c>
       <c r="B5" t="n">
-        <v>79881</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,38 +1053,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>512908</v>
+        <v>513031</v>
       </c>
       <c r="R5" t="n">
-        <v>6702264</v>
+        <v>6702372</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1127,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,7 +1137,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,6 +1151,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1146,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123219686</v>
+        <v>123218719</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>79882</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,52 +1182,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513016</v>
+        <v>512908</v>
       </c>
       <c r="R6" t="n">
-        <v>6702423</v>
+        <v>6702264</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1245,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,12 +1255,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1277,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123219381</v>
+        <v>123219686</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,12 +1317,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1325,21 +1330,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Torpsjön, Torpsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513011</v>
+        <v>513016</v>
       </c>
       <c r="R7" t="n">
-        <v>6702358</v>
+        <v>6702423</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en yta av ca 10x10m</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD7" t="b">
